--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -30847,6 +30847,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1326">
+      <c r="A1326" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1326" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1326" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1326" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -30870,6 +30870,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1327">
+      <c r="A1327" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1327" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1327" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1327" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -30893,6 +30893,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1328">
+      <c r="A1328" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1328" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1328" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1328" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1328" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -30916,6 +30916,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1329">
+      <c r="A1329" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1329" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1329" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1329" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1329" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -30780,7 +30780,7 @@
     </row>
     <row r="1323">
       <c r="A1323" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1323" t="n">
         <v>0</v>
@@ -30803,7 +30803,7 @@
     </row>
     <row r="1324">
       <c r="A1324" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1324" t="n">
         <v>0</v>
@@ -30826,7 +30826,7 @@
     </row>
     <row r="1325">
       <c r="A1325" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1325" t="n">
         <v>0</v>
@@ -30849,7 +30849,7 @@
     </row>
     <row r="1326">
       <c r="A1326" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1326" t="n">
         <v>0</v>
@@ -30872,7 +30872,7 @@
     </row>
     <row r="1327">
       <c r="A1327" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1327" t="n">
         <v>0</v>
@@ -30895,7 +30895,7 @@
     </row>
     <row r="1328">
       <c r="A1328" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1328" t="n">
         <v>0</v>
@@ -30918,24 +30918,47 @@
     </row>
     <row r="1329">
       <c r="A1329" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1329" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1329" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1329" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1329" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="1" t="n">
         <v>46281.2916666667</v>
       </c>
-      <c r="B1329" t="n">
-        <v>0</v>
-      </c>
-      <c r="C1329" t="n">
-        <v>0.218999996781349</v>
-      </c>
-      <c r="D1329" t="n">
-        <v>0.218999996781349</v>
-      </c>
-      <c r="E1329" t="n">
-        <v>0.218999996781349</v>
-      </c>
-      <c r="F1329" t="n">
-        <v>0.218999996781349</v>
-      </c>
-      <c r="G1329" t="s">
+      <c r="B1330" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1330" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1330" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -30962,6 +30962,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1331">
+      <c r="A1331" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1331" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1331" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1331" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1331" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1331" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1332" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1332" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1332" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31008,6 +31008,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1333">
+      <c r="A1333" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B1333" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1333" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1333" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31031,6 +31031,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1334">
+      <c r="A1334" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1334" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1334" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1334" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31054,6 +31054,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1335">
+      <c r="A1335" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1335" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1335" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1335" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31077,6 +31077,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1336">
+      <c r="A1336" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1336" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1336" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1336" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31100,6 +31100,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1337">
+      <c r="A1337" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1337" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1337" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1337" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31123,6 +31123,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1338">
+      <c r="A1338" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B1338" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1338" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1338" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1338" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31146,6 +31146,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1339">
+      <c r="A1339" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B1339" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1339" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1339" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1339" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1339" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1339" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31169,6 +31169,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1340">
+      <c r="A1340" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1340" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1340" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1340" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1340" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31192,6 +31192,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1341">
+      <c r="A1341" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B1341" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1341" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1341" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1341" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1341" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1341" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31215,6 +31215,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1342">
+      <c r="A1342" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1342" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1342" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1342" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1342" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31238,6 +31238,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1343">
+      <c r="A1343" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1343" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1343" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1343" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1343" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1343" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1343" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31261,6 +31261,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1344">
+      <c r="A1344" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1344" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1344" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1344" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1344" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1344" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1344" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31284,6 +31284,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1345">
+      <c r="A1345" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1345" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1345" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1345" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1345" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1345" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1345" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31307,6 +31307,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1346">
+      <c r="A1346" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1346" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1346" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1346" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1346" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1346" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1346" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31353,6 +31353,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1348">
+      <c r="A1348" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1348" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1348" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1348" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1348" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1348" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1348" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31376,6 +31376,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1349">
+      <c r="A1349" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1349" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1349" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1349" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1349" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1349" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1349" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31399,6 +31399,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1350">
+      <c r="A1350" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B1350" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1350" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1350" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1350" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1350" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1350" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -31422,6 +31422,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1351">
+      <c r="A1351" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1351" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1351" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1351" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1351" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1351" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -39586,6 +39586,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1353">
+      <c r="A1353" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1353" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1353" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1353" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1353" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="H1353" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1353" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -39615,6 +39615,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1354">
+      <c r="A1354" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1354" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1354" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1354" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1354" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="H1354" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1354" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -39644,6 +39644,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1355">
+      <c r="A1355" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1355" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1355" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1355" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1355" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1355" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1355" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="H1355" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1355" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -39673,6 +39673,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1356">
+      <c r="A1356" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1356" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1356" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1356" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1356" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="H1356" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1356" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -39702,6 +39702,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1357">
+      <c r="A1357" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1357" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1357" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1357" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1357" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="H1357" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1357" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -39731,6 +39731,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1358">
+      <c r="A1358" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1358" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1358" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1358" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1358" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="H1358" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1358" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -39760,6 +39760,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1359">
+      <c r="A1359" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1359" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1359" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1359" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1359" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1359" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="H1359" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1359" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -39789,6 +39789,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1360">
+      <c r="A1360" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1360" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1360" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1360" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1360" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="H1360" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1360" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MQSPA.MI.xlsx
+++ b/data/MQSPA.MI.xlsx
@@ -39818,6 +39818,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1361">
+      <c r="A1361" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1361" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1361" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="F1361" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="G1361" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="H1361" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1361" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
